--- a/repo/inputs/Permits to Ride.xlsx
+++ b/repo/inputs/Permits to Ride.xlsx
@@ -8,7 +8,6 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smida\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D119814-CEAF-4A47-9EFA-155E6BB73CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A6430D89-0652-48A3-AD7C-B545602393AD}"/>
   </bookViews>
